--- a/output/pdf_financials_xlsx/NET.UN.xlsx
+++ b/output/pdf_financials_xlsx/NET.UN.xlsx
@@ -7217,7 +7217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7418,17 +7418,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charges financières                                            142,067        163,818                                             Financial expenses</t>
+          <t>Portion à court terme des emprunts hypothécaires et</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Charges financières                                            142,067        163,818                                             Financial expenses total</t>
+          <t>Portion à court terme des emprunts hypothécaires et iide la dette à long terme 16 179 507 13 804 643 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -7462,32 +7462,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="5" t="n">
+        <v>0.864</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>10698.442</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>11885.327</v>
+        <v>0.374</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>de placement                                                                                   -     12,473,198                                     investment properties</t>
+          <t>Emprunts hypothécaires sur des immeubles de</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>de placement                                                                                   -     12,473,198                                     investment properties total</t>
+          <t>Total des capitaux propres 129 440 950 129 487 381 (46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -7527,26 +7527,28 @@
         </is>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3718.653</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>-11336.409</v>
+        <v>0.431</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Émission de débentures convertibles,                                                                             Issuance of convertible debentures,</t>
+          <t>Emprunts hypothécaires sur des immeubles de</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Émission de débentures convertibles,                                                                             Issuance of convertible debentures, total</t>
+          <t>Nb. moyen pondéré de parts en circulation de base 20 553 943 20 566 316 (12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -7586,26 +7588,28 @@
         </is>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-14478.701</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>-949.0119999999999</v>
+        <v>0.373</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charges financières                                            163,818         (19,670)                                             Financial expenses</t>
+          <t>FPEA (1)                                                       0.564               0.570              (0.006)     (1%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charges financières                                            163,818         (19,670)                                             Financial expenses total</t>
+          <t>Distributions 0.345 0.345</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -7639,11 +7643,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K7" s="5" t="n">
-        <v>11034.527</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>10698.442</v>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7654,17 +7662,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>de placement                                              12,473,198      4,234,268                                     investment properties</t>
+          <t>100%           100%                           -</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>de placement                                              12,473,198      4,234,268                                     investment properties total</t>
+          <t>Nombre de propriétés 94</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -7699,10 +7707,10 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>2713.694</v>
+        <v>-0.004</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>3718.653</v>
+        <v>0.098</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7713,17 +7721,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Rachats de parts                                                                                 -        (500,877)                                    Repurchase of units</t>
+          <t>Autre</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rachats de parts                                                                                 -        (500,877)                                    Repurchase of units total</t>
+          <t>Durée résiduelle moyenne pondérée - hypothèques 3.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -7758,10 +7766,10 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-13184.081</v>
+        <v>-0.0007</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-14478.701</v>
+        <v>0.0046</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7772,17 +7780,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ajustements:                                                                                                 Adjustments</t>
+          <t>Autre</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Impôts différés                                                         (7 500)        (18 125)                                       Deferred income taxes</t>
+          <t>Durée résiduelle moyenne pondérée - baux 6.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -7806,21 +7814,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>0.000849</v>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>9.1e-05</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-0.0005</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>0.0065</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7836,12 +7844,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ajustements:                                                                                                 Adjustments</t>
+          <t>Charges financières                                            142,067        163,818                                             Financial expenses</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>de l'actif et du passif (note 21)                              (515 663)        97 088                                        liability items (note 21)</t>
+          <t>Charges financières                                            142,067        163,818                                             Financial expenses total</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -7865,26 +7873,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>0.000937</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>0.000188</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L11" s="5" t="n">
+        <v>10698.442</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>11885.327</v>
       </c>
     </row>
     <row r="12">
@@ -7895,12 +7903,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ACTIVITÉS D'INVESTISSEMENT                                                               INVESTING ACTIVITIES</t>
+          <t>de placement                                                                                   -     12,473,198                                     investment properties</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Encaissement des prêts à recevoir                             413 034      2 410 000                             Proceeds from loans receivable</t>
+          <t>de placement                                                                                   -     12,473,198                                     investment properties total</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -7924,26 +7932,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>0.000359</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0.000829</v>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L12" s="5" t="n">
+        <v>3718.653</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>-11336.409</v>
       </c>
     </row>
     <row r="13">
@@ -7954,12 +7962,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Emprunts hypothécaires:                                                                                                                Mortgages</t>
+          <t>Émission de débentures convertibles,                                                                             Issuance of convertible debentures,</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Distributions aux porteurs de parts                                 (2 457 083)      (1 834 111)                                        Distributions to unitholders</t>
+          <t>Émission de débentures convertibles,                                                                             Issuance of convertible debentures, total</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -7983,26 +7991,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>0.000441</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>0.000535</v>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L13" s="5" t="n">
+        <v>-14478.701</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>-949.0119999999999</v>
       </c>
     </row>
     <row r="14">
@@ -8013,12 +8021,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Charges financières                                        73 055        (145 568)                                           Financial expenses</t>
+          <t>Charges financières                                            163,818         (19,670)                                             Financial expenses</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Impôts différés                                                  (18 125)         3 425                                     Deferred income taxes</t>
+          <t>Charges financières                                            163,818         (19,670)                                             Financial expenses total</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -8037,26 +8045,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n">
-        <v>0.000197</v>
-      </c>
-      <c r="I14" s="5" t="n">
-        <v>7.8e-05</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K14" s="5" t="n">
+        <v>11034.527</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>10698.442</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8072,12 +8080,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Charges financières                                        73 055        (145 568)                                           Financial expenses</t>
+          <t>de placement                                              12,473,198      4,234,268                                     investment properties</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>de l'actif et du passif (note 21)                           97 088          (18 049)                                    liability items (note 21)</t>
+          <t>de placement                                              12,473,198      4,234,268                                     investment properties total</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -8096,26 +8104,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H15" s="5" t="n">
-        <v>0.000148</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>6e-05</v>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K15" s="5" t="n">
+        <v>2713.694</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>3718.653</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -8131,12 +8139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ACTIVITÉS D'INVESTISSEMENT                                                            INVESTING ACTIVITIES</t>
+          <t>Rachats de parts                                                                                 -        (500,877)                                    Repurchase of units</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Encaissement des prêts à recevoir                         2 410 000                       -                            Cash in of loans receivable</t>
+          <t>Rachats de parts                                                                                 -        (500,877)                                    Repurchase of units total</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -8155,26 +8163,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H16" s="5" t="n">
-        <v>0.0009840000000000001</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>0.0009840000000000001</v>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K16" s="5" t="n">
+        <v>-13184.081</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>-14478.701</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -8190,12 +8198,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emprunts hypothécaires:                                                                                                            Mortgages</t>
+          <t>Ajustements:                                                                                                 Adjustments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Distributions aux porteurs de parts                               (1 834 111)       (1 277 539)                                      Distributions to unitholders</t>
+          <t>Impôts différés                                                         (7 500)        (18 125)                                       Deferred income taxes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -8214,16 +8222,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H17" s="5" t="n">
-        <v>0.000182</v>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.000139</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000849</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>9.1e-05</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -8249,12 +8257,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Charges financières                                         (145 568)        92 190                                             Financial expenses</t>
+          <t>Ajustements:                                                                                                 Adjustments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Impôts différés                                            3 425         18 000                                      Deferred income taxes</t>
+          <t>de l'actif et du passif (note 21)                              (515 663)        97 088                                        liability items (note 21)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -8268,21 +8276,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n">
-        <v>0.000388</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>0.000165</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>0.000937</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>0.000188</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -8308,12 +8316,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Charges financières                                         (145 568)        92 190                                             Financial expenses</t>
+          <t>ACTIVITÉS D'INVESTISSEMENT                                                               INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>de l'actif et du passif (note 24)                             (18 049)       254 050                                      liability items (note 24)</t>
+          <t>Encaissement des prêts à recevoir                             413 034      2 410 000                             Proceeds from loans receivable</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -8327,21 +8335,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="5" t="n">
-        <v>0.000438</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>0.000419</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>0.000359</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>0.000829</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -8367,12 +8375,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ACTIVITÉS D'INVESTISSEMENT                                                            INVESTING ACTIVITIES</t>
+          <t>Emprunts hypothécaires:                                                                                                                Mortgages</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prêts à recevoir (note 7)                                        (1 460 000)                      -                                Loans receivable (note 7)</t>
+          <t>Distributions aux porteurs de parts                                 (2 457 083)      (1 834 111)                                        Distributions to unitholders</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -8386,21 +8394,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="5" t="n">
-        <v>0.000326</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>0.000541</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>0.000441</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>0.000535</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -8426,12 +8434,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Remboursements d'emprunts                                                         -       (3 876 389)                                     Mortgages repaid</t>
+          <t>Charges financières                                        73 055        (145 568)                                           Financial expenses</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Distributions aux porteurs de parts                              (1 277 539)        (851 796)                                       Distributions to unitholders</t>
+          <t>Impôts différés                                                  (18 125)         3 425                                     Deferred income taxes</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -8445,16 +8453,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G21" s="5" t="n">
-        <v>0.000878</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.000139</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000197</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>7.8e-05</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -8485,35 +8493,35 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Variation de la juste valeur des</t>
+          <t>Charges financières                                        73 055        (145 568)                                           Financial expenses</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Impôts sur le résultat                         43 700       31 739        43 700        31 739   Income taxes</t>
+          <t>de l'actif et du passif (note 21)                           97 088          (18 049)                                    liability items (note 21)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" s="5" t="n">
-        <v>4.7e-05</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.000147</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H22" s="5" t="n">
+        <v>0.000148</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>6e-05</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -8544,35 +8552,35 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Variation de la juste valeur des</t>
+          <t>ACTIVITÉS D'INVESTISSEMENT                                                            INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>de l'actif et du passif (note 16)              (29 028)      28 747        (25 247)       17 574    liability items (note 16)</t>
+          <t>Encaissement des prêts à recevoir                         2 410 000                       -                            Cash in of loans receivable</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="n">
-        <v>0.000621</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>0.000164</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H23" s="5" t="n">
+        <v>0.0009840000000000001</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>0.0009840000000000001</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -8603,35 +8611,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ACTIVITÉS DE FINANCEMENT                                                FINANCING ACTIVITIES</t>
+          <t>Emprunts hypothécaires:                                                                                                            Mortgages</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Frais d'émission de parts / d'actions              (16 463)                  -        (16 463)        (35 250)   Units / Shares issue costs</t>
+          <t>Distributions aux porteurs de parts                               (1 834 111)       (1 277 539)                                      Distributions to unitholders</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" s="5" t="n">
-        <v>0.0005730000000000001</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>0.000358</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H24" s="5" t="n">
+        <v>0.000182</v>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>0.000139</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -8657,17 +8665,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>immeubles de placement                                    3,044,899      (4,755,298)                                                      properties</t>
+          <t>Charges financières                                         (145 568)        92 190                                             Financial expenses</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>immeubles de placement                                    3,044,899      (4,755,298)                                                      properties total</t>
+          <t>Impôts différés                                            3 425         18 000                                      Deferred income taxes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -8681,15 +8689,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G25" s="5" t="n">
+        <v>0.000388</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.000165</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -8706,34 +8710,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L25" s="5" t="n">
-        <v>16024.145</v>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v>26399.868</v>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHARGES                                                                                 EXPENSES</t>
+          <t>Charges financières                                         (145 568)        92 190                                             Financial expenses</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CHARGES                                                                                 EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>de l'actif et du passif (note 24)                             (18 049)       254 050                                      liability items (note 24)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -8744,15 +8748,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G26" s="5" t="n">
+        <v>0.000438</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.000419</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -8769,27 +8769,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L26" s="5" t="n">
-        <v>9017.928</v>
-      </c>
-      <c r="M26" s="5" t="n">
-        <v>9390.424000000001</v>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DES CAPITAUX PROPRES                                                                     CHANGES IN EQUITY</t>
+          <t>ACTIVITÉS D'INVESTISSEMENT                                                            INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2025 DECEMBER</t>
+          <t>Prêts à recevoir (note 7)                                        (1 460 000)                      -                                Loans receivable (note 7)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -8803,15 +8807,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G27" s="5" t="n">
+        <v>0.000326</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.000541</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -8828,27 +8828,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n">
-        <v>2.025</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>0.031</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Earnings                                    Equity</t>
+          <t>Remboursements d'emprunts                                                         -       (3 876 389)                                     Mortgages repaid</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1er janvier 2025 26,327,972 103,041,578 71,400 129,440,950 January</t>
+          <t>Distributions aux porteurs de parts                              (1 277 539)        (851 796)                                       Distributions to unitholders</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -8862,15 +8866,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G28" s="5" t="n">
+        <v>0.000878</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.000139</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -8887,39 +8887,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L28" s="5" t="n">
-        <v>2.025</v>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v>0.001</v>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Earnings                                    Equity</t>
+          <t>Variation de la juste valeur des</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>31 décembre 2025 35,845,913 103,249,335 71,400 139,166,648 December</t>
+          <t>Impôts sur le résultat                         43 700       31 739        43 700        31 739   Income taxes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="5" t="n">
+        <v>4.7e-05</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.000147</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -8946,39 +8946,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L29" s="5" t="n">
-        <v>2.025</v>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v>0.031</v>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Earnings                                    Equity</t>
+          <t>Variation de la juste valeur des</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2024 DECEMBER</t>
+          <t>de l'actif et du passif (note 16)              (29 028)      28 747        (25 247)       17 574    liability items (note 16)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" s="5" t="n">
+        <v>0.000621</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.000164</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -9005,39 +9005,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L30" s="5" t="n">
-        <v>2.024</v>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v>0.031</v>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Earnings                                    Equity</t>
+          <t>ACTIVITÉS DE FINANCEMENT                                                FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1er janvier 2024 26,315,569 103,100,412 71,400 129,487,381 January</t>
+          <t>Frais d'émission de parts / d'actions              (16 463)                  -        (16 463)        (35 250)   Units / Shares issue costs</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="5" t="n">
+        <v>0.0005730000000000001</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.000358</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -9059,14 +9059,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K31" s="5" t="n">
-        <v>2.024</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>2.024</v>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v>0.001</v>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -9077,12 +9083,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coûts d'émission                                                                (217,392)                                  (217,392)                                         Issue costs</t>
+          <t>immeubles de placement                                    3,044,899      (4,755,298)                                                      properties</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>31 décembre 2024 26,327,972 103,041,578 71,400 129,440,950 December</t>
+          <t>immeubles de placement                                    3,044,899      (4,755,298)                                                      properties total</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -9122,10 +9128,10 @@
         </is>
       </c>
       <c r="L32" s="5" t="n">
-        <v>2.024</v>
+        <v>16024.145</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0.031</v>
+        <v>26399.868</v>
       </c>
     </row>
     <row r="33">
@@ -9136,15 +9142,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>immeubles de placement                                       (4,755,298)      4,319,072                                                        properties</t>
+          <t>CHARGES                                                                                 EXPENSES</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>immeubles de placement                                       (4,755,298)      4,319,072                                                        properties total</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>CHARGES                                                                                 EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -9175,16 +9185,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K33" s="5" t="n">
-        <v>26828.073</v>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L33" s="5" t="n">
-        <v>16024.145</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9017.928</v>
+      </c>
+      <c r="M33" s="5" t="n">
+        <v>9390.424000000001</v>
       </c>
     </row>
     <row r="34">
@@ -9195,19 +9205,15 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CHARGES                                                                                  EXPENSES</t>
+          <t>DES CAPITAUX PROPRES                                                                     CHANGES IN EQUITY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CHARGES                                                                                  EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>31 DÉCEMBRE 2025 DECEMBER</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -9238,16 +9244,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="5" t="n">
-        <v>8600.152</v>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L34" s="5" t="n">
-        <v>9017.928</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.025</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>0.031</v>
       </c>
     </row>
     <row r="35">
@@ -9258,12 +9264,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DES CAPITAUX PROPRES                                                                     CHANGES IN EQUITY</t>
+          <t>Earnings                                    Equity</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2024 DECEMBER</t>
+          <t>1er janvier 2025 26,327,972 103,041,578 71,400 129,440,950 January</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
@@ -9297,16 +9303,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K35" s="5" t="n">
-        <v>2.024</v>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.025</v>
+      </c>
+      <c r="M35" s="5" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="36">
@@ -9317,12 +9323,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Coûts d'émission                                                                       -             (217,392)                            -             (217,392)                                         Issue costs</t>
+          <t>Earnings                                    Equity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>31 décembre 2024 26,327,972 103,041,578 71,400 129,440,950 December</t>
+          <t>31 décembre 2025 35,845,913 103,249,335 71,400 139,166,648 December</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -9356,16 +9362,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K36" s="5" t="n">
-        <v>2.024</v>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L36" s="5" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="M36" s="5" t="n">
         <v>0.031</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="37">
@@ -9376,12 +9382,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coûts d'émission                                                                       -             (217,392)                            -             (217,392)                                         Issue costs</t>
+          <t>Earnings                                    Equity</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2023 DECEMBER</t>
+          <t>31 DÉCEMBRE 2024 DECEMBER</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -9415,16 +9421,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K37" s="5" t="n">
-        <v>2.023</v>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L37" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="M37" s="5" t="n">
         <v>0.031</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="38">
@@ -9440,7 +9446,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1er janvier 2023 15,190,642 103,425,725 71,400 118,687,767 January</t>
+          <t>1er janvier 2024 26,315,569 103,100,412 71,400 129,487,381 January</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -9475,15 +9481,13 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>2.023</v>
+        <v>2.024</v>
       </c>
       <c r="L38" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="M38" s="5" t="n">
         <v>0.001</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="39">
@@ -9494,12 +9498,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coûts d'émission                                                                       -              (25,736)                            -              (25,736)                                         Issue costs</t>
+          <t>Coûts d'émission                                                                (217,392)                                  (217,392)                                         Issue costs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>31 décembre 2023 26,315,569 103,100,412 71,400 129,487,381 December</t>
+          <t>31 décembre 2024 26,327,972 103,041,578 71,400 129,440,950 December</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -9533,16 +9537,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K39" s="5" t="n">
-        <v>2.023</v>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L39" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="M39" s="5" t="n">
         <v>0.031</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
     </row>
     <row r="40">
@@ -9553,12 +9557,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Autres produits                                                                                 -        15 000                                              Other revenues</t>
+          <t>immeubles de placement                                       (4,755,298)      4,319,072                                                        properties</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>immeubles de placement                               1 546 054      (4 862 229)                                                      properties</t>
+          <t>immeubles de placement                                       (4,755,298)      4,319,072                                                        properties total</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -9582,21 +9586,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="5" t="n">
-        <v>0.000304</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>0.000268</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>26828.073</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>16024.145</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -9612,15 +9616,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Charges administratives                                   627 894       536 021                                           Administrative expenses</t>
+          <t>CHARGES                                                                                  EXPENSES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charges financières (note 18)                              3 583 094     1 602 914                                       Financial expenses (note 18)</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>CHARGES                                                                                  EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -9641,21 +9649,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="5" t="n">
-        <v>0.00056</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>0.000175</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>8600.152</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>9017.928</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -9671,12 +9679,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DES CAPITAUX PROPRES                                                                    CHANGES IN EQUITY</t>
+          <t>DES CAPITAUX PROPRES                                                                     CHANGES IN EQUITY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2019 DECEMBER</t>
+          <t>31 DÉCEMBRE 2024 DECEMBER</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -9700,21 +9708,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -9728,10 +9736,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Coûts d'émission                                                                       -             (217,392)                            -             (217,392)                                         Issue costs</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1er janvier 2019 1 869 427 39 361 322 71 400 41 302 149 January</t>
+          <t>31 décembre 2024 26,327,972 103,041,578 71,400 129,440,950 December</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -9755,21 +9767,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -9783,10 +9795,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Coûts d'émission                                                                       -             (217,392)                            -             (217,392)                                         Issue costs</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>31 décembre 2019 3 272 356 47 998 284 71 400 51 342 040 December</t>
+          <t>31 DÉCEMBRE 2023 DECEMBER</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -9810,21 +9826,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I44" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -9838,10 +9854,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Earnings                                    Equity</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2018 DECEMBER</t>
+          <t>1er janvier 2023 15,190,642 103,425,725 71,400 118,687,767 January</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -9865,21 +9885,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I45" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>0.001</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -9893,10 +9913,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Coûts d'émission                                                                       -              (25,736)                            -              (25,736)                                         Issue costs</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1er janvier 2018 5 914 073 30 722 923 71 400 36 708 396 January</t>
+          <t>31 décembre 2023 26,315,569 103,100,412 71,400 129,487,381 December</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -9920,21 +9944,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -9948,10 +9972,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Autres produits                                                                                 -        15 000                                              Other revenues</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>31 décembre 2018 1 869 427 39 361 322 71 400 41 302 149 December</t>
+          <t>immeubles de placement                               1 546 054      (4 862 229)                                                      properties</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -9976,10 +10004,10 @@
         </is>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0.002018</v>
+        <v>0.000304</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.000268</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -10005,12 +10033,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Autres revenus                                           15 000        10 000                                             Other revenues</t>
+          <t>Charges administratives                                   627 894       536 021                                           Administrative expenses</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>immeubles de placement                                     (3 871 418)     2 174 622                                                      properties</t>
+          <t>Charges financières (note 18)                              3 583 094     1 602 914                                       Financial expenses (note 18)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -10029,16 +10057,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H48" s="5" t="n">
-        <v>0.00014</v>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I48" s="5" t="n">
-        <v>0.000895</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.00056</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>0.000175</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -10064,12 +10092,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Charges administratives                                   536 021       517 824                                         Administrative expenses</t>
+          <t>DES CAPITAUX PROPRES                                                                    CHANGES IN EQUITY</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charges financières (note 18)                             1 602 914       791 702                                     Financial expenses (note 18)</t>
+          <t>31 DÉCEMBRE 2019 DECEMBER</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -10088,16 +10116,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H49" s="5" t="n">
-        <v>0.000771</v>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0.00035</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002019</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -10121,14 +10149,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>DES CAPITAUX PROPRES                                                                    CHANGES IN EQUITY</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2018 DECEMBER</t>
+          <t>1er janvier 2019 1 869 427 39 361 322 71 400 41 302 149 January</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -10147,16 +10171,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H50" s="5" t="n">
-        <v>0.002018</v>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I50" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002019</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -10183,7 +10207,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1 janvier 2018 5 914 073 30 722 923 71 400 36 708 396 January</t>
+          <t>31 décembre 2019 3 272 356 47 998 284 71 400 51 342 040 December</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -10202,16 +10226,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H51" s="5" t="n">
-        <v>0.002018</v>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I51" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002019</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -10238,7 +10262,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>31 décembre 2018 2 860 238 39 361 322 71 400 42 292 960 December</t>
+          <t>31 DÉCEMBRE 2018 DECEMBER</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -10257,16 +10281,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H52" s="5" t="n">
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="n">
         <v>0.002018</v>
       </c>
-      <c r="I52" s="5" t="n">
+      <c r="J52" s="5" t="n">
         <v>3.1e-05</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -10293,7 +10317,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2017 DECEMBER</t>
+          <t>1er janvier 2018 5 914 073 30 722 923 71 400 36 708 396 January</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -10312,16 +10336,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H53" s="5" t="n">
-        <v>0.002017</v>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I53" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002018</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -10348,7 +10372,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1 janvier 2017 2 902 914 18 444 994 71 400 21 419 308 January</t>
+          <t>31 décembre 2018 1 869 427 39 361 322 71 400 41 302 149 December</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -10362,19 +10386,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>0.002017</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>0.002017</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I54" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002018</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -10398,10 +10424,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Autres revenus                                           15 000        10 000                                             Other revenues</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>31 décembre 2017 5 914 073 30 722 923 71 400 36 708 396 December</t>
+          <t>immeubles de placement                                     (3 871 418)     2 174 622                                                      properties</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -10415,14 +10445,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G55" s="5" t="n">
-        <v>0.002017</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.002017</v>
+        <v>0.00014</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.000895</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -10453,12 +10485,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Autres revenus                                         10 000       155 350                                           Other revenues</t>
+          <t>Charges administratives                                   536 021       517 824                                         Administrative expenses</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>immeubles de placement                             2 174 622     2 088 379                                                    properties</t>
+          <t>Charges financières (note 18)                             1 602 914       791 702                                     Financial expenses (note 18)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -10472,16 +10504,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G56" s="5" t="n">
-        <v>0.000417</v>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.000763</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000771</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>0.00035</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -10512,12 +10544,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Charges administratives                                 559 069       472 400                                        Administrative expenses</t>
+          <t>DES CAPITAUX PROPRES                                                                    CHANGES IN EQUITY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pénalités sur annulation de dette (note 10)                                        -       239 992                     Debt extinguishment penalties (note 10)</t>
+          <t>31 DÉCEMBRE 2018 DECEMBER</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -10531,16 +10563,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n">
-        <v>0.000598</v>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.000548</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002018</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -10569,14 +10601,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>DES CAPITAUX PROPRES                                                                    CHANGES IN EQUITY</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2017 DECEMBER</t>
+          <t>1 janvier 2018 5 914 073 30 722 923 71 400 36 708 396 January</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -10590,16 +10618,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G58" s="5" t="n">
-        <v>0.002017</v>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H58" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002018</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -10631,7 +10659,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2016 DECEMBER</t>
+          <t>31 décembre 2018 2 860 238 39 361 322 71 400 42 292 960 December</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -10645,16 +10673,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n">
-        <v>0.002016</v>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H59" s="5" t="n">
+        <v>0.002018</v>
+      </c>
+      <c r="I59" s="5" t="n">
         <v>3.1e-05</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -10686,7 +10714,7 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1 janvier 2016 646 803 13 422 994 71 400 14 141 197 January</t>
+          <t>31 DÉCEMBRE 2017 DECEMBER</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -10700,16 +10728,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" s="5" t="n">
-        <v>0.002016</v>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H60" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002017</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -10741,7 +10769,7 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>31 décembre 2016 2 902 914 18 444 994 71 400 21 419 308 December</t>
+          <t>1 janvier 2017 2 902 914 18 444 994 71 400 21 419 308 January</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -10756,15 +10784,13 @@
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.002016</v>
+        <v>0.002017</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002017</v>
+      </c>
+      <c r="I61" s="5" t="n">
+        <v>1e-06</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -10793,37 +10819,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CHARGES                                                          EXPENSES</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charges financières (notes 15 et 19)             91 195       15 456      298 376      217 337    Financial expenses (notes 15 and 19)</t>
+          <t>31 décembre 2017 5 914 073 30 722 923 71 400 36 708 396 December</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.000665</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>0.000369</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.002017</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0.002017</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -10854,30 +10874,30 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DES CAPITAUX PROPRES                                            CHANGES IN EQUITY</t>
+          <t>Autres revenus                                         10 000       155 350                                           Other revenues</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2011 DECEMBER</t>
+          <t>immeubles de placement                             2 174 622     2 088 379                                                    properties</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>0.002011</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.000417</v>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>0.000763</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -10913,30 +10933,30 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>fondée sur des parts suite                                                                                    compensation following</t>
+          <t>Charges administratives                                 559 069       472 400                                        Administrative expenses</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>31 décembre 2011 (133 748) 4 871 000 71 400 4 808 652 December</t>
+          <t>Pénalités sur annulation de dette (note 10)                                        -       239 992                     Debt extinguishment penalties (note 10)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>0.002011</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.000598</v>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>0.000548</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -10972,30 +10992,30 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>fondée sur des parts suite                                                                                    compensation following</t>
+          <t>DES CAPITAUX PROPRES                                                                    CHANGES IN EQUITY</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>31 DÉCEMBRE 2010 DECEMBER</t>
+          <t>31 DÉCEMBRE 2017 DECEMBER</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" s="5" t="n">
-        <v>0.00201</v>
-      </c>
-      <c r="F65" s="5" t="n">
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.002017</v>
+      </c>
+      <c r="H65" s="5" t="n">
         <v>3.1e-05</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -11032,47 +11052,448 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
+          <t>31 DÉCEMBRE 2016 DECEMBER</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.002016</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1 janvier 2016 646 803 13 422 994 71 400 14 141 197 January</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.002016</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>31 décembre 2016 2 902 914 18 444 994 71 400 21 419 308 December</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.002016</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CHARGES                                                          EXPENSES</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Charges financières (notes 15 et 19)             91 195       15 456      298 376      217 337    Financial expenses (notes 15 and 19)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>0.000665</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0.000369</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DES CAPITAUX PROPRES                                            CHANGES IN EQUITY</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>31 DÉCEMBRE 2011 DECEMBER</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>0.002011</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>fondée sur des parts suite                                                                                    compensation following</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>31 décembre 2011 (133 748) 4 871 000 71 400 4 808 652 December</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" s="5" t="n">
+        <v>0.002011</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>fondée sur des parts suite                                                                                    compensation following</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>31 DÉCEMBRE 2010 DECEMBER</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>0.00201</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>31 décembre 2010 (14 894) 3 190 000 73 900 3 249 006 December</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
         <v>0.00201</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F73" s="5" t="n">
         <v>3.1e-05</v>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t>-</t>
         </is>
